--- a/output/2026-09-02_03_Italia_Abruzzo_Componentistica_Ventilazione_industriale.xlsx
+++ b/output/2026-09-02_03_Italia_Abruzzo_Componentistica_Ventilazione_industriale.xlsx
@@ -494,10 +494,9 @@
           <t>085 8000096 / 085 8008850</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Verificato tramite PagineGialle/PagineBianche/sito ufficiale. Distributore ingrosso/dettaglio di ricambi industriali generalisti (oleodinamica, pneumatica, cuscinetti, compressori, trasmissioni; marchi ABAC, Camozzi, SKF, Waircom). Coerente come canale B2B di componentistica industriale, non specializzato esclusivamente su ventilazione.</t>
+          <t>Verificato tramite PagineGialle/PagineBianche/sito ufficiale. Distributore ingrosso/dettaglio di ricambi industriali generalisti (oleodinamica, pneumatica, cuscinetti, compressori, trasmissioni; marchi ABAC, Camozzi, SKF, Waircom). Coerente come canale B2B di componentistica industriale, non specializzato esclusivamente su ventilazione. [DUPLICATO — vedi anche: 2026-09-02_00_Italia_Abruzzo_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -581,7 +580,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Verificato tramite sito ufficiale e fonti terze. Vendita e assistenza (rivenditore multi-marca) di compressori, idropulitrici, aspiratori ed elettroutensili per aziende.</t>
+          <t>Verificato tramite sito ufficiale e fonti terze. Vendita e assistenza (rivenditore multi-marca) di compressori, idropulitrici, aspiratori ed elettroutensili per aziende. [DUPLICATO — vedi anche: 2026-09-02_00_Italia_Abruzzo_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -658,10 +657,9 @@
           <t>0871 561812</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Verificato: azienda dal 1974, ~25 dipendenti, 2000 mq, forniture industriali (cuscinetti, trasmissioni, oleodinamica, utensili, DPI, aspiratori industriali per trucioli/polveri/liquidi). Solido distributore B2B.</t>
+          <t>Verificato: azienda dal 1974, ~25 dipendenti, 2000 mq, forniture industriali (cuscinetti, trasmissioni, oleodinamica, utensili, DPI, aspiratori industriali per trucioli/polveri/liquidi). Solido distributore B2B. [DUPLICATO — vedi anche: 2026-09-02_00_Italia_Abruzzo_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
